--- a/analysis/statistics/Cross_Flavor_Comparisons.xlsx
+++ b/analysis/statistics/Cross_Flavor_Comparisons.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="90" uniqueCount="10">
   <si>
     <t>Comparison</t>
   </si>
@@ -91,11 +91,11 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="76.85546875" customWidth="true"/>
-    <col min="2" max="2" width="15.140625" customWidth="true"/>
-    <col min="3" max="3" width="14.42578125" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="8.42578125" customWidth="true"/>
+    <col min="1" max="1" width="70.6640625" customWidth="true"/>
+    <col min="2" max="2" width="14.5546875" customWidth="true"/>
+    <col min="3" max="3" width="14.21875" customWidth="true"/>
+    <col min="4" max="4" width="12.5546875" customWidth="true"/>
+    <col min="5" max="5" width="7.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -123,13 +123,13 @@
         <v>0.48740797391785307</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.075042485050014207</v>
+        <v>-0.078114210106988824</v>
       </c>
       <c r="D2" s="0">
-        <v>1.1238413119966939</v>
+        <v>1.1048498799423909</v>
       </c>
       <c r="E2" s="0">
-        <v>0.089599999999999999</v>
+        <v>0.095600000000000004</v>
       </c>
     </row>
     <row r="3">
@@ -140,13 +140,13 @@
         <v>0.0043553078311378002</v>
       </c>
       <c r="C3" s="0">
-        <v>-0.51020795587640322</v>
+        <v>-0.52378900973888376</v>
       </c>
       <c r="D3" s="0">
-        <v>0.57808634046587137</v>
+        <v>0.57408347828464279</v>
       </c>
       <c r="E3" s="0">
-        <v>0.96460000000000001</v>
+        <v>0.98040000000000005</v>
       </c>
     </row>
     <row r="4">
@@ -157,13 +157,13 @@
         <v>0.22460386994645098</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.54335349962053214</v>
+        <v>-0.53650951082908793</v>
       </c>
       <c r="D4" s="0">
-        <v>0.94372210471671325</v>
+        <v>0.91766617988629096</v>
       </c>
       <c r="E4" s="0">
-        <v>0.52300000000000002</v>
+        <v>0.53939999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -174,13 +174,13 @@
         <v>0.24666395972148625</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.61214514562978217</v>
+        <v>-0.59750804267485391</v>
       </c>
       <c r="D5" s="0">
-        <v>0.9764811938702036</v>
+        <v>0.96208390098370833</v>
       </c>
       <c r="E5" s="0">
-        <v>0.63759999999999995</v>
+        <v>0.64800000000000002</v>
       </c>
     </row>
   </sheetData>
